--- a/para-evaluacion-1/Sin título 2.xlsx
+++ b/para-evaluacion-1/Sin título 2.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Hoja1_2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Hoja3" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="24">
   <si>
     <t xml:space="preserve">EL alfabeto es {0,1}</t>
   </si>
@@ -48,6 +49,51 @@
   </si>
   <si>
     <t xml:space="preserve">estado recuperable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lenguaje (e) {w : w comienza en 1 y tiene longitud impar, o empieza en 0 y tiene longitud par}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">el alfabeto es {0,1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comienza en 1 y tiene longitud impar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estado inicial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estado aceptacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comienza en 0 y tiene longitud par</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estado no recuparable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estado recuperable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">esta mal por que acepta la cadena vacia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de ahora en adelante me referirie a los estados de este afd como a,b, c,d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reconocer todo el lenguaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epsilon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alfa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estados iniciales de los otros dos automatas : a y E1</t>
   </si>
 </sst>
 </file>
@@ -129,7 +175,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -143,10 +189,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -446,7 +488,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="4"/>
+      <c r="C16" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -457,4 +499,258 @@
     <oddFooter>&amp;CPágina &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="76.28"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/para-evaluacion-1/Sin título 2.xlsx
+++ b/para-evaluacion-1/Sin título 2.xlsx
@@ -10,7 +10,8 @@
   <sheets>
     <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Hoja1_2" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Hoja3" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="intento custom afn a afd" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Hoja3" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="40">
   <si>
     <t xml:space="preserve">EL alfabeto es {0,1}</t>
   </si>
@@ -51,6 +52,66 @@
     <t xml:space="preserve">estado recuperable</t>
   </si>
   <si>
+    <t xml:space="preserve">aqui intentare convertir este AFN a AFD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caracter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epsilon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A,B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unica transicion epsilon es de B a C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">por lo tanto, reemplazo b por b,c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A,{B,C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B,C]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ahora el siguiente paso , voy desde el estrado inicial a cada conjunto de estado posible por cada transicion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estado inicial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A,B,C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A,D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estado aceptacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">muerto</t>
+  </si>
+  <si>
     <t xml:space="preserve">lenguaje (e) {w : w comienza en 1 y tiene longitud impar, o empieza en 0 y tiene longitud par}</t>
   </si>
   <si>
@@ -60,12 +121,6 @@
     <t xml:space="preserve">comienza en 1 y tiene longitud impar</t>
   </si>
   <si>
-    <t xml:space="preserve">estado inicial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estado aceptacion</t>
-  </si>
-  <si>
     <t xml:space="preserve">comienza en 0 y tiene longitud par</t>
   </si>
   <si>
@@ -84,13 +139,7 @@
     <t xml:space="preserve">reconocer todo el lenguaje</t>
   </si>
   <si>
-    <t xml:space="preserve">epsilon</t>
-  </si>
-  <si>
     <t xml:space="preserve">alfa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nada</t>
   </si>
   <si>
     <t xml:space="preserve">estados iniciales de los otros dos automatas : a y E1</t>
@@ -506,242 +555,497 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:H44"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C2" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F7" s="0" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E8" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E9" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E11" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E12" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F28" s="0" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E29" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E30" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E31" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E32" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E33" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F39" s="0" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E40" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D41" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G41" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E42" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="0" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D43" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F43" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G43" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E44" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G44" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:F31"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="76.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="76.28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>9</v>
+      <c r="A1" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>10</v>
+      <c r="A3" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>11</v>
+      <c r="A5" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="F20" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>23</v>
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -749,8 +1053,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>